--- a/results/All_spectra_areas.xlsx
+++ b/results/All_spectra_areas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,286 +466,286 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.913</v>
+        <v>-8.044499999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2390661740876158</v>
+        <v>0.2237569162714261</v>
       </c>
       <c r="E2" t="n">
-        <v>510.863519375325</v>
+        <v>510.9675463112821</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06767582226982673</v>
+        <v>0.05486782228419522</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04055473862534937</v>
+        <v>0.03077401248242342</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9531476038610569</v>
+        <v>0.9044561961446524</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003074440474462207</v>
+        <v>0.000422872735633458</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="C3" t="n">
-        <v>-6.1535</v>
+        <v>-7.161</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4740603280196903</v>
+        <v>0.2080982106503001</v>
       </c>
       <c r="E3" t="n">
-        <v>510.827251766163</v>
+        <v>510.9069611448738</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04979295169949224</v>
+        <v>0.08022382213500635</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05916861705402011</v>
+        <v>0.04184673988684305</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9733140909269358</v>
+        <v>0.9220477193899147</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006626791279422031</v>
+        <v>0.0004167339879425213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.3785</v>
+        <v>-6.262</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7518191566375469</v>
+        <v>0.4665646122511978</v>
       </c>
       <c r="E4" t="n">
-        <v>510.7598291403203</v>
+        <v>510.8303015694486</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05106863385302875</v>
+        <v>0.05080276454813937</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09624043156163267</v>
+        <v>0.05941403884000665</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9833178082631966</v>
+        <v>0.9575956421521898</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009870730030696114</v>
+        <v>0.001017629949792184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="C5" t="n">
-        <v>-4.619</v>
+        <v>-5.363</v>
       </c>
       <c r="D5" t="n">
-        <v>1.854313810153958</v>
+        <v>0.7691649595444319</v>
       </c>
       <c r="E5" t="n">
-        <v>510.7385075831388</v>
+        <v>510.7591072148255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0499458925721055</v>
+        <v>0.05083234813739867</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2321522759225413</v>
+        <v>0.09800530783377533</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9974478657917766</v>
+        <v>0.984326177777005</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001062049451302711</v>
+        <v>0.0009759712598858959</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.844</v>
+        <v>-4.4795</v>
       </c>
       <c r="D6" t="n">
-        <v>5.216724994870361</v>
+        <v>2.202980112786467</v>
       </c>
       <c r="E6" t="n">
-        <v>510.7086330574284</v>
+        <v>510.7332973260663</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05619300592605231</v>
+        <v>0.05111033168635706</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7348016817278979</v>
+        <v>0.2822339215328761</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9993014139541561</v>
+        <v>0.9979705534315033</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002094672344268421</v>
+        <v>0.001184658363058574</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.0845</v>
+        <v>-3.5805</v>
       </c>
       <c r="D7" t="n">
-        <v>22.6160548909478</v>
+        <v>7.958706828300113</v>
       </c>
       <c r="E7" t="n">
-        <v>510.6734908336385</v>
+        <v>510.6937256660767</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05117664792434563</v>
+        <v>0.05881827866614767</v>
       </c>
       <c r="G7" t="n">
-        <v>2.901206353528314</v>
+        <v>1.173396401048514</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9986666092060925</v>
+        <v>0.9991901989411479</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06860231076922783</v>
+        <v>0.005731087706657812</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.3095</v>
+        <v>-2.6815</v>
       </c>
       <c r="D8" t="n">
-        <v>104.9765550401442</v>
+        <v>54.01635707670143</v>
       </c>
       <c r="E8" t="n">
-        <v>510.6587748773402</v>
+        <v>510.66491394339</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04906522510922159</v>
+        <v>0.04888622221856495</v>
       </c>
       <c r="G8" t="n">
-        <v>12.91088600349006</v>
+        <v>6.619142079480369</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9996381078238054</v>
+        <v>0.9993769748695236</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4562431969663817</v>
+        <v>0.1937243995844966</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.55</v>
+        <v>-1.798</v>
       </c>
       <c r="D9" t="n">
-        <v>253.2442265642054</v>
+        <v>203.0620857470633</v>
       </c>
       <c r="E9" t="n">
-        <v>510.6503196555607</v>
+        <v>510.6525001069126</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05082047149719882</v>
+        <v>0.05022107013148074</v>
       </c>
       <c r="G9" t="n">
-        <v>32.26028332967373</v>
+        <v>25.56258323656836</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9997782831907589</v>
+        <v>0.9997469446478555</v>
       </c>
       <c r="I9" t="n">
-        <v>1.740807444449116</v>
+        <v>1.260756139644606</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.775</v>
+        <v>-0.899</v>
       </c>
       <c r="D10" t="n">
-        <v>371.8135678858603</v>
+        <v>357.9521294235789</v>
       </c>
       <c r="E10" t="n">
-        <v>510.6481568243464</v>
+        <v>510.648154349946</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05218126737477386</v>
+        <v>0.05196591255943969</v>
       </c>
       <c r="G10" t="n">
-        <v>48.63285781566669</v>
+        <v>46.62656723016049</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9998096996046398</v>
+        <v>0.9998085081863815</v>
       </c>
       <c r="I10" t="n">
-        <v>3.257859088826703</v>
+        <v>3.036104844738616</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -755,28 +755,28 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>404.8201656605372</v>
+        <v>404.8201663755487</v>
       </c>
       <c r="E11" t="n">
-        <v>510.6519940612459</v>
+        <v>510.6519940612486</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0530655897738474</v>
+        <v>0.05306558968664842</v>
       </c>
       <c r="G11" t="n">
-        <v>53.84744084158462</v>
+        <v>53.84744084820864</v>
       </c>
       <c r="H11" t="n">
-        <v>0.999729455372533</v>
+        <v>0.9997284130474761</v>
       </c>
       <c r="I11" t="n">
-        <v>5.430739303686399</v>
+        <v>5.450752260157421</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -786,28 +786,28 @@
         <v>0.6355</v>
       </c>
       <c r="D12" t="n">
-        <v>377.0353044341849</v>
+        <v>377.0353045615936</v>
       </c>
       <c r="E12" t="n">
-        <v>510.6599255855314</v>
+        <v>510.6599255855353</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05418277675941359</v>
+        <v>0.05418277670690604</v>
       </c>
       <c r="G12" t="n">
-        <v>51.2074571539989</v>
+        <v>51.20745712167884</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9993549212410194</v>
+        <v>0.9993535512696889</v>
       </c>
       <c r="I12" t="n">
-        <v>10.82147820916992</v>
+        <v>10.84252768712496</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -817,524 +817,524 @@
         <v>1.2865</v>
       </c>
       <c r="D13" t="n">
-        <v>292.3431310341022</v>
+        <v>292.3431090998706</v>
       </c>
       <c r="E13" t="n">
-        <v>510.6685535060276</v>
+        <v>510.6685535046393</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05436776285495953</v>
+        <v>0.05436777013053583</v>
       </c>
       <c r="G13" t="n">
-        <v>39.84045512635353</v>
+        <v>39.84045746867106</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9972713331060582</v>
+        <v>0.9972686891825497</v>
       </c>
       <c r="I13" t="n">
-        <v>25.86520612332151</v>
+        <v>25.8831884106103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C14" t="n">
-        <v>1.922</v>
+        <v>1.9375</v>
       </c>
       <c r="D14" t="n">
-        <v>171.6000662386687</v>
+        <v>168.3471206741532</v>
       </c>
       <c r="E14" t="n">
-        <v>510.6781490599487</v>
+        <v>510.6785248668766</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05888326202096811</v>
+        <v>0.05920648299598811</v>
       </c>
       <c r="G14" t="n">
-        <v>25.32790370822458</v>
+        <v>24.98416795429241</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9894878037881827</v>
+        <v>0.9893084849133894</v>
       </c>
       <c r="I14" t="n">
-        <v>35.22304107725829</v>
+        <v>34.63438911825934</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C15" t="n">
-        <v>2.573</v>
+        <v>2.5885</v>
       </c>
       <c r="D15" t="n">
-        <v>66.97361708134544</v>
+        <v>65.51660981281236</v>
       </c>
       <c r="E15" t="n">
-        <v>510.7105664478796</v>
+        <v>510.7115298383762</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07050033528032869</v>
+        <v>0.07029614011641674</v>
       </c>
       <c r="G15" t="n">
-        <v>11.83545262342228</v>
+        <v>11.54443890660009</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9988278060136994</v>
+        <v>0.9989378747453092</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7125625060842843</v>
+        <v>0.6163465807292631</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C16" t="n">
-        <v>3.2085</v>
+        <v>3.2395</v>
       </c>
       <c r="D16" t="n">
-        <v>24.3716129511554</v>
+        <v>22.99371333904723</v>
       </c>
       <c r="E16" t="n">
-        <v>510.7377653419459</v>
+        <v>510.7385754468974</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05900681884964985</v>
+        <v>0.05872672633228624</v>
       </c>
       <c r="G16" t="n">
-        <v>3.604760440621981</v>
+        <v>3.384814237454327</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9923796424595231</v>
+        <v>0.9916246838307363</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5648207632816773</v>
+        <v>0.5503809075537289</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C17" t="n">
-        <v>3.8595</v>
+        <v>3.8905</v>
       </c>
       <c r="D17" t="n">
-        <v>6.821162949146901</v>
+        <v>6.377841841055338</v>
       </c>
       <c r="E17" t="n">
-        <v>510.7587159851951</v>
+        <v>510.7601613107805</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06031428797367473</v>
+        <v>0.06126829366766321</v>
       </c>
       <c r="G17" t="n">
-        <v>1.031260928313301</v>
+        <v>0.9794887784029546</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9656448864212679</v>
+        <v>0.9617558830506163</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1925055357970792</v>
+        <v>0.1858725213704898</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C18" t="n">
-        <v>4.495</v>
+        <v>4.5415</v>
       </c>
       <c r="D18" t="n">
-        <v>2.372705730028968</v>
+        <v>2.290014567947091</v>
       </c>
       <c r="E18" t="n">
-        <v>510.8153966698769</v>
+        <v>510.8200053856243</v>
       </c>
       <c r="F18" t="n">
-        <v>0.07096371068829736</v>
+        <v>0.06897808506396735</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4220560498245861</v>
+        <v>0.3959490568576285</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9967833865734295</v>
+        <v>0.9804925884161285</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002411275898695247</v>
+        <v>0.01302549727556506</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C19" t="n">
-        <v>5.146</v>
+        <v>5.1925</v>
       </c>
       <c r="D19" t="n">
-        <v>1.522107602369676</v>
+        <v>1.4478444652217</v>
       </c>
       <c r="E19" t="n">
-        <v>510.8452679472288</v>
+        <v>510.8459721990726</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05065508533309068</v>
+        <v>0.0514382751448753</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1932672826921182</v>
+        <v>0.1866801931700975</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9943225619861393</v>
+        <v>0.9658667605696231</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001541474431117754</v>
+        <v>0.008035643997791378</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cu I 510.5</t>
+          <t>Cu I 510.5 nm</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C20" t="n">
-        <v>5.797</v>
+        <v>5.8435</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4758370424794044</v>
+        <v>0.3149259405080001</v>
       </c>
       <c r="E20" t="n">
-        <v>511.0863072004093</v>
+        <v>510.9201414737282</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1992099035575814</v>
+        <v>0.1026317638005022</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2376069321257795</v>
+        <v>0.08101774699925234</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9647727616104489</v>
+        <v>0.9022038046030946</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0005901902592761766</v>
+        <v>0.001373082818854875</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="C21" t="n">
-        <v>-3.782</v>
+        <v>-4.0765</v>
       </c>
       <c r="D21" t="n">
-        <v>0.450054669388352</v>
+        <v>0.3083587316597143</v>
       </c>
       <c r="E21" t="n">
-        <v>515.4628138309413</v>
+        <v>515.4684917508231</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05645256254063087</v>
+        <v>0.0586098882986907</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06368525127189716</v>
+        <v>0.04530196899741011</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9515275547100478</v>
+        <v>0.9014014749432129</v>
       </c>
       <c r="I21" t="n">
-        <v>0.00108039412114577</v>
+        <v>0.0009853771063458086</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="C22" t="n">
-        <v>-3.3635</v>
+        <v>-3.627</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8972749737729903</v>
+        <v>0.5890583819792972</v>
       </c>
       <c r="E22" t="n">
-        <v>515.4568250703657</v>
+        <v>515.4619848935695</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05320382415499172</v>
+        <v>0.0537163612265289</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1196625734310651</v>
+        <v>0.07931491442339721</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9867503512282688</v>
+        <v>0.967825472539103</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001205670522724927</v>
+        <v>0.001241856805377746</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="C23" t="n">
-        <v>-2.945</v>
+        <v>-3.1775</v>
       </c>
       <c r="D23" t="n">
-        <v>2.608671868791667</v>
+        <v>1.384386507814723</v>
       </c>
       <c r="E23" t="n">
-        <v>515.4453008731197</v>
+        <v>515.4503047970617</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05311048792637415</v>
+        <v>0.05302492406492171</v>
       </c>
       <c r="G23" t="n">
-        <v>0.347287922583485</v>
+        <v>0.1840040353193765</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9978618757109674</v>
+        <v>0.9939107166684956</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001600014005078956</v>
+        <v>0.001298520056936716</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="C24" t="n">
-        <v>-2.5265</v>
+        <v>-2.728</v>
       </c>
       <c r="D24" t="n">
-        <v>8.556634698673633</v>
+        <v>4.97464135510773</v>
       </c>
       <c r="E24" t="n">
-        <v>515.4347470315994</v>
+        <v>515.4398664740531</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05601331277239545</v>
+        <v>0.05416571712027841</v>
       </c>
       <c r="G24" t="n">
-        <v>1.201390474766576</v>
+        <v>0.6754235628885127</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9992743559151516</v>
+        <v>0.9989674486277533</v>
       </c>
       <c r="I24" t="n">
-        <v>0.005794317024083796</v>
+        <v>0.002770115736649686</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C25" t="n">
-        <v>-2.108</v>
+        <v>-2.2785</v>
       </c>
       <c r="D25" t="n">
-        <v>21.24435075316614</v>
+        <v>15.17417836513582</v>
       </c>
       <c r="E25" t="n">
-        <v>515.4253613459041</v>
+        <v>515.4289552391818</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05906094805949592</v>
+        <v>0.05824746727296538</v>
       </c>
       <c r="G25" t="n">
-        <v>3.145095313356896</v>
+        <v>2.215502094257879</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9997238350263865</v>
+        <v>0.9995950450349298</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01410873111536383</v>
+        <v>0.0104412550778823</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.6895</v>
+        <v>-1.8135</v>
       </c>
       <c r="D26" t="n">
-        <v>39.94388067656678</v>
+        <v>33.97290288200802</v>
       </c>
       <c r="E26" t="n">
-        <v>515.4185580103549</v>
+        <v>515.4202944014008</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06015403121020955</v>
+        <v>0.06011956073094622</v>
       </c>
       <c r="G26" t="n">
-        <v>6.022889933995712</v>
+        <v>5.119627821764674</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9999008648856226</v>
+        <v>0.9998650642172052</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0182797465073296</v>
+        <v>0.01797078575540138</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.271</v>
+        <v>-1.364</v>
       </c>
       <c r="D27" t="n">
-        <v>59.84914969080054</v>
+        <v>55.6832965904695</v>
       </c>
       <c r="E27" t="n">
-        <v>515.4155097688177</v>
+        <v>515.4155518689619</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06048080470017651</v>
+        <v>0.06040251892209206</v>
       </c>
       <c r="G27" t="n">
-        <v>9.073304364427393</v>
+        <v>8.430822054172575</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9998852998243315</v>
+        <v>0.9998841759869722</v>
       </c>
       <c r="I27" t="n">
-        <v>0.04784415280051969</v>
+        <v>0.0417586296662406</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.8525</v>
+        <v>-0.9145</v>
       </c>
       <c r="D28" t="n">
-        <v>77.03606279179088</v>
+        <v>74.74897868593263</v>
       </c>
       <c r="E28" t="n">
-        <v>515.4163450741705</v>
+        <v>515.4161099495128</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06074779673444185</v>
+        <v>0.06075949972267893</v>
       </c>
       <c r="G28" t="n">
-        <v>11.73044651719649</v>
+        <v>11.38438007916432</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9998990912569087</v>
+        <v>0.9999002863669053</v>
       </c>
       <c r="I28" t="n">
-        <v>0.07005663766591413</v>
+        <v>0.06520695890528898</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.434</v>
+        <v>-0.465</v>
       </c>
       <c r="D29" t="n">
-        <v>86.85574930592588</v>
+        <v>86.50789545748869</v>
       </c>
       <c r="E29" t="n">
-        <v>515.4183487528055</v>
+        <v>515.418078900693</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06093410212488497</v>
+        <v>0.0609061130967484</v>
       </c>
       <c r="G29" t="n">
-        <v>13.26627273753782</v>
+        <v>13.20707261008721</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9999012912152606</v>
+        <v>0.9999035413417234</v>
       </c>
       <c r="I29" t="n">
-        <v>0.08734235142788468</v>
+        <v>0.08463590075301412</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1365,565 +1365,565 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C31" t="n">
-        <v>0.372</v>
+        <v>0.3875</v>
       </c>
       <c r="D31" t="n">
-        <v>83.72735582335488</v>
+        <v>83.44071664568082</v>
       </c>
       <c r="E31" t="n">
-        <v>515.4280019066526</v>
+        <v>515.4282592940494</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06184924230444519</v>
+        <v>0.06183805609816688</v>
       </c>
       <c r="G31" t="n">
-        <v>12.98050813921848</v>
+        <v>12.93372994112039</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9998817110239533</v>
+        <v>0.9998832310425974</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09947280641800794</v>
+        <v>0.0975480476697846</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7595</v>
+        <v>0.7905</v>
       </c>
       <c r="D32" t="n">
-        <v>71.08485107015457</v>
+        <v>69.62871672011775</v>
       </c>
       <c r="E32" t="n">
-        <v>515.4346146938898</v>
+        <v>515.4351395897295</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06218786711638089</v>
+        <v>0.06229257369977403</v>
       </c>
       <c r="G32" t="n">
-        <v>11.0808392329093</v>
+        <v>10.87212907978617</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9998617396099251</v>
+        <v>0.9998586887565309</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08529833602930822</v>
+        <v>0.08387317942301116</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C33" t="n">
-        <v>1.147</v>
+        <v>1.1935</v>
       </c>
       <c r="D33" t="n">
-        <v>53.77438934744543</v>
+        <v>51.74693544031476</v>
       </c>
       <c r="E33" t="n">
-        <v>515.4425917921457</v>
+        <v>515.4436641206553</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06242641237328577</v>
+        <v>0.0623509388531041</v>
       </c>
       <c r="G33" t="n">
-        <v>8.414606246165123</v>
+        <v>8.087560947984704</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9997775110047932</v>
+        <v>0.9997590796621345</v>
       </c>
       <c r="I33" t="n">
-        <v>0.08029498037232523</v>
+        <v>0.08064620385422401</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C34" t="n">
-        <v>1.5345</v>
+        <v>1.5965</v>
       </c>
       <c r="D34" t="n">
-        <v>37.80006152992827</v>
+        <v>35.37777586919074</v>
       </c>
       <c r="E34" t="n">
-        <v>515.4529971388235</v>
+        <v>515.4545578287025</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06039191034665525</v>
+        <v>0.05979133183592704</v>
       </c>
       <c r="G34" t="n">
-        <v>5.722175961686517</v>
+        <v>5.302231527035304</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9994530266141406</v>
+        <v>0.9993587566458246</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09799272028026818</v>
+        <v>0.1004806823266971</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="C35" t="n">
-        <v>1.922</v>
+        <v>1.9995</v>
       </c>
       <c r="D35" t="n">
-        <v>23.02587791747881</v>
+        <v>20.32428635307543</v>
       </c>
       <c r="E35" t="n">
-        <v>515.462896588375</v>
+        <v>515.4643968221339</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05687673455871701</v>
+        <v>0.05631193324015793</v>
       </c>
       <c r="G35" t="n">
-        <v>3.282772497755951</v>
+        <v>2.868835700033077</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9987770305498098</v>
+        <v>0.9985800570256356</v>
       </c>
       <c r="I35" t="n">
-        <v>0.08101110570620784</v>
+        <v>0.07318923288084977</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="C36" t="n">
-        <v>2.3095</v>
+        <v>2.4025</v>
       </c>
       <c r="D36" t="n">
-        <v>11.08234350270223</v>
+        <v>8.882036356147328</v>
       </c>
       <c r="E36" t="n">
-        <v>515.4690684233545</v>
+        <v>515.470537702583</v>
       </c>
       <c r="F36" t="n">
-        <v>0.05458962936242039</v>
+        <v>0.05429765445738002</v>
       </c>
       <c r="G36" t="n">
-        <v>1.516462541074325</v>
+        <v>1.208880995162233</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9970784208347656</v>
+        <v>0.9963542038793302</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04432867894928823</v>
+        <v>0.03536721823736196</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="C37" t="n">
-        <v>2.697</v>
+        <v>2.8055</v>
       </c>
       <c r="D37" t="n">
-        <v>3.714590443596201</v>
+        <v>2.645026815102573</v>
       </c>
       <c r="E37" t="n">
-        <v>515.4770116841406</v>
+        <v>515.4815423703548</v>
       </c>
       <c r="F37" t="n">
-        <v>0.05492559464143825</v>
+        <v>0.05568782022143339</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5114175633593548</v>
+        <v>0.3692157612677387</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9914152942107172</v>
+        <v>0.989416065078745</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01412437338189033</v>
+        <v>0.008652791716140964</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="C38" t="n">
-        <v>3.0845</v>
+        <v>3.2085</v>
       </c>
       <c r="D38" t="n">
-        <v>1.116933742823683</v>
+        <v>0.7635009450009297</v>
       </c>
       <c r="E38" t="n">
-        <v>515.4931475976949</v>
+        <v>515.499720760012</v>
       </c>
       <c r="F38" t="n">
-        <v>0.05797849912947748</v>
+        <v>0.06092704100864307</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1623245898399751</v>
+        <v>0.1166029665730118</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9771643545078299</v>
+        <v>0.9636951688860828</v>
       </c>
       <c r="I38" t="n">
-        <v>0.003119815787252536</v>
+        <v>0.00232485514015044</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cu I 515.3</t>
+          <t>Cu I 515.3 nm</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="C39" t="n">
-        <v>3.472</v>
+        <v>3.6115</v>
       </c>
       <c r="D39" t="n">
-        <v>0.359532892062322</v>
+        <v>0.2430707681131056</v>
       </c>
       <c r="E39" t="n">
-        <v>515.5147018830593</v>
+        <v>515.5303030986906</v>
       </c>
       <c r="F39" t="n">
-        <v>0.07224779480562794</v>
+        <v>0.0766829532025245</v>
       </c>
       <c r="G39" t="n">
-        <v>0.06511081900232536</v>
+        <v>0.04672200779862996</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9507719625028412</v>
+        <v>0.9045375035586904</v>
       </c>
       <c r="I39" t="n">
-        <v>0.000753151589138314</v>
+        <v>0.000643667150906459</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C40" t="n">
-        <v>-3.5805</v>
+        <v>-3.782</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5789940369554957</v>
+        <v>0.4199572055323004</v>
       </c>
       <c r="E40" t="n">
-        <v>521.9374112237858</v>
+        <v>521.9461910781246</v>
       </c>
       <c r="F40" t="n">
-        <v>0.06664190203676368</v>
+        <v>0.07339584429308524</v>
       </c>
       <c r="G40" t="n">
-        <v>0.09671891345242307</v>
+        <v>0.07726208822988725</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9509234567904443</v>
+        <v>0.9097665536782382</v>
       </c>
       <c r="I40" t="n">
-        <v>0.00168095153237303</v>
+        <v>0.001626387138281063</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C41" t="n">
-        <v>-3.193</v>
+        <v>-3.3635</v>
       </c>
       <c r="D41" t="n">
-        <v>1.367235917764693</v>
+        <v>0.8801844284400192</v>
       </c>
       <c r="E41" t="n">
-        <v>521.9259051816119</v>
+        <v>521.9321061809808</v>
       </c>
       <c r="F41" t="n">
-        <v>0.06019592288461464</v>
+        <v>0.06241369373709399</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2063005901205131</v>
+        <v>0.1377030313596643</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9717128324776985</v>
+        <v>0.9766900643854698</v>
       </c>
       <c r="I41" t="n">
-        <v>0.005496198754889371</v>
+        <v>0.001870941482443762</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>-2.79</v>
+        <v>-2.945</v>
       </c>
       <c r="D42" t="n">
-        <v>4.697428894793798</v>
+        <v>2.831753697625</v>
       </c>
       <c r="E42" t="n">
-        <v>521.9168235224665</v>
+        <v>521.9199042446537</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05697590059376224</v>
+        <v>0.05870002545699638</v>
       </c>
       <c r="G42" t="n">
-        <v>0.670874597414761</v>
+        <v>0.4166618137623053</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9815010479976755</v>
+        <v>0.9788157687885369</v>
       </c>
       <c r="I42" t="n">
-        <v>0.04392385992943958</v>
+        <v>0.01815977514306261</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C43" t="n">
-        <v>-2.387</v>
+        <v>-2.5265</v>
       </c>
       <c r="D43" t="n">
-        <v>15.85033607083632</v>
+        <v>10.75579661044097</v>
       </c>
       <c r="E43" t="n">
-        <v>521.9117444919864</v>
+        <v>521.9133810521764</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05675515834270811</v>
+        <v>0.0565684231341886</v>
       </c>
       <c r="G43" t="n">
-        <v>2.254933552242819</v>
+        <v>1.525129031679619</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9858008594753355</v>
+        <v>0.9855588555815845</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3927573716788403</v>
+        <v>0.1828170277030899</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.9995</v>
+        <v>-2.108</v>
       </c>
       <c r="D44" t="n">
-        <v>37.21156156673396</v>
+        <v>30.26790500071314</v>
       </c>
       <c r="E44" t="n">
-        <v>521.9068931988271</v>
+        <v>521.9081763400145</v>
       </c>
       <c r="F44" t="n">
-        <v>0.05838646177454381</v>
+        <v>0.05786527107781778</v>
       </c>
       <c r="G44" t="n">
-        <v>5.446029472737211</v>
+        <v>4.390260480943528</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9859200366189862</v>
+        <v>0.9857089643091458</v>
       </c>
       <c r="I44" t="n">
-        <v>2.172437311615098</v>
+        <v>1.454471274009233</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.5965</v>
+        <v>-1.6895</v>
       </c>
       <c r="D45" t="n">
-        <v>68.72065195359083</v>
+        <v>61.03017614994414</v>
       </c>
       <c r="E45" t="n">
-        <v>521.9032223777001</v>
+        <v>521.9037966068796</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05939878542951328</v>
+        <v>0.05917710192698811</v>
       </c>
       <c r="G45" t="n">
-        <v>10.23186425830874</v>
+        <v>9.052910990063898</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9860658928124818</v>
+        <v>0.9861552337171586</v>
       </c>
       <c r="I45" t="n">
-        <v>7.35896079418907</v>
+        <v>5.76190899334831</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.1935</v>
+        <v>-1.271</v>
       </c>
       <c r="D46" t="n">
-        <v>101.4297452865129</v>
+        <v>95.63586735836755</v>
       </c>
       <c r="E46" t="n">
-        <v>521.9021824803154</v>
+        <v>521.9022419454454</v>
       </c>
       <c r="F46" t="n">
-        <v>0.06015180348364318</v>
+        <v>0.05999659845582891</v>
       </c>
       <c r="G46" t="n">
-        <v>15.29339557524722</v>
+        <v>14.38259872105119</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9861711311434628</v>
+        <v>0.9861956294131908</v>
       </c>
       <c r="I46" t="n">
-        <v>15.97327477217384</v>
+        <v>14.16079222264987</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.806</v>
+        <v>-0.8525</v>
       </c>
       <c r="D47" t="n">
-        <v>126.9677949549035</v>
+        <v>124.6072975173957</v>
       </c>
       <c r="E47" t="n">
-        <v>521.9023104064438</v>
+        <v>521.9022413907059</v>
       </c>
       <c r="F47" t="n">
-        <v>0.06059465022172519</v>
+        <v>0.06052598649582049</v>
       </c>
       <c r="G47" t="n">
-        <v>19.28491790084145</v>
+        <v>18.90493932914184</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9863017833536279</v>
+        <v>0.9863778372763761</v>
       </c>
       <c r="I47" t="n">
-        <v>24.86157082827709</v>
+        <v>23.80125557310719</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.403</v>
+        <v>-0.434</v>
       </c>
       <c r="D48" t="n">
-        <v>142.4545527577422</v>
+        <v>141.6908814230629</v>
       </c>
       <c r="E48" t="n">
-        <v>521.9034838404502</v>
+        <v>521.9032998992595</v>
       </c>
       <c r="F48" t="n">
-        <v>0.06111793510939113</v>
+        <v>0.0610426694944868</v>
       </c>
       <c r="G48" t="n">
-        <v>21.824029538118</v>
+        <v>21.68030331702964</v>
       </c>
       <c r="H48" t="n">
-        <v>0.986492958600766</v>
+        <v>0.9864954066293574</v>
       </c>
       <c r="I48" t="n">
-        <v>31.00649846076614</v>
+        <v>30.6480573495612</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1954,280 +1954,1458 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3875</v>
+        <v>0.4185</v>
       </c>
       <c r="D50" t="n">
-        <v>135.7567342785981</v>
+        <v>134.5605805905812</v>
       </c>
       <c r="E50" t="n">
-        <v>521.9103709567241</v>
+        <v>521.9107656174205</v>
       </c>
       <c r="F50" t="n">
-        <v>0.06282432016754108</v>
+        <v>0.0628805259901723</v>
       </c>
       <c r="G50" t="n">
-        <v>21.37859273937167</v>
+        <v>21.20918363569952</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9854709345817662</v>
+        <v>0.9853587463473089</v>
       </c>
       <c r="I50" t="n">
-        <v>30.67206707261169</v>
+        <v>30.37202401141113</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C51" t="n">
-        <v>0.775</v>
+        <v>0.837</v>
       </c>
       <c r="D51" t="n">
-        <v>116.8784018070819</v>
+        <v>112.9707078834801</v>
       </c>
       <c r="E51" t="n">
-        <v>521.9158589007259</v>
+        <v>521.9169043755696</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06301533370334762</v>
+        <v>0.06288322008840765</v>
       </c>
       <c r="G51" t="n">
-        <v>18.46164684569434</v>
+        <v>17.80699172880794</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9838934442937239</v>
+        <v>0.9835931475625349</v>
       </c>
       <c r="I51" t="n">
-        <v>25.11191002993632</v>
+        <v>23.83923532533704</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="C52" t="n">
-        <v>1.178</v>
+        <v>1.271</v>
       </c>
       <c r="D52" t="n">
-        <v>89.92091773048202</v>
+        <v>83.80643678461308</v>
       </c>
       <c r="E52" t="n">
-        <v>521.9230355211902</v>
+        <v>521.9248363023695</v>
       </c>
       <c r="F52" t="n">
-        <v>0.06188896104249125</v>
+        <v>0.06138425338391677</v>
       </c>
       <c r="G52" t="n">
-        <v>13.94966752766092</v>
+        <v>12.89508734349586</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9805097965858388</v>
+        <v>0.9795571254045407</v>
       </c>
       <c r="I52" t="n">
-        <v>17.58311823725549</v>
+        <v>15.87628048476898</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="C53" t="n">
-        <v>1.5655</v>
+        <v>1.6895</v>
       </c>
       <c r="D53" t="n">
-        <v>63.69555940808647</v>
+        <v>55.15913417549837</v>
       </c>
       <c r="E53" t="n">
-        <v>521.9312052413821</v>
+        <v>521.9341410054296</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06079813240894372</v>
+        <v>0.06086422896104629</v>
       </c>
       <c r="G53" t="n">
-        <v>9.70709610136543</v>
+        <v>8.415297993415061</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9753304765784189</v>
+        <v>0.9736319405652498</v>
       </c>
       <c r="I53" t="n">
-        <v>10.80364903558231</v>
+        <v>8.59646369701122</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="C54" t="n">
-        <v>1.953</v>
+        <v>2.1235</v>
       </c>
       <c r="D54" t="n">
-        <v>36.80636349388993</v>
+        <v>26.19763846897984</v>
       </c>
       <c r="E54" t="n">
-        <v>521.9410603046734</v>
+        <v>521.9470774781956</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06312015904089713</v>
+        <v>0.06780178751772645</v>
       </c>
       <c r="G54" t="n">
-        <v>5.823457757131373</v>
+        <v>4.45239024340226</v>
       </c>
       <c r="H54" t="n">
-        <v>0.970203623064584</v>
+        <v>0.9710698142117742</v>
       </c>
       <c r="I54" t="n">
-        <v>4.405233344230868</v>
+        <v>2.311061670886623</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="C55" t="n">
-        <v>2.356</v>
+        <v>2.542</v>
       </c>
       <c r="D55" t="n">
-        <v>15.59775079408423</v>
+        <v>10.04159548925909</v>
       </c>
       <c r="E55" t="n">
-        <v>521.9582407151743</v>
+        <v>521.9698008676507</v>
       </c>
       <c r="F55" t="n">
-        <v>0.07389253697559536</v>
+        <v>0.07493046515880537</v>
       </c>
       <c r="G55" t="n">
-        <v>2.889032910044627</v>
+        <v>1.886040808183146</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9787171420024897</v>
+        <v>0.9871818219374192</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6494819833987588</v>
+        <v>0.1628872825101531</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="C56" t="n">
-        <v>2.7435</v>
+        <v>2.976</v>
       </c>
       <c r="D56" t="n">
-        <v>6.095403133070165</v>
+        <v>3.296230979817694</v>
       </c>
       <c r="E56" t="n">
-        <v>521.9823991320978</v>
+        <v>521.9934892802613</v>
       </c>
       <c r="F56" t="n">
-        <v>0.07050478040723453</v>
+        <v>0.06273146554355265</v>
       </c>
       <c r="G56" t="n">
-        <v>1.077236183034407</v>
+        <v>0.5183140777306336</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9880560721537328</v>
+        <v>0.9812674750788014</v>
       </c>
       <c r="I56" t="n">
-        <v>0.05310862575204532</v>
+        <v>0.02255343500852792</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>742</v>
+        <v>759</v>
       </c>
       <c r="C57" t="n">
-        <v>3.131</v>
+        <v>3.3945</v>
       </c>
       <c r="D57" t="n">
-        <v>2.146124108573103</v>
+        <v>1.170698990648787</v>
       </c>
       <c r="E57" t="n">
-        <v>521.9997237487514</v>
+        <v>522.0099319571377</v>
       </c>
       <c r="F57" t="n">
-        <v>0.05949954744387112</v>
+        <v>0.05398010114491161</v>
       </c>
       <c r="G57" t="n">
-        <v>0.3200799200575843</v>
+        <v>0.1584049949829296</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9782081464871457</v>
+        <v>0.9630319818727324</v>
       </c>
       <c r="I57" t="n">
-        <v>0.01084589793048291</v>
+        <v>0.005176818796530954</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cu I 521.8</t>
+          <t>Cu I 521.8 nm</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>768</v>
+        <v>787</v>
       </c>
       <c r="C58" t="n">
-        <v>3.534</v>
+        <v>3.8285</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9056093877679801</v>
+        <v>0.5008102366384638</v>
       </c>
       <c r="E58" t="n">
-        <v>522.0149262584234</v>
+        <v>522.0162801193337</v>
       </c>
       <c r="F58" t="n">
-        <v>0.05141823570485177</v>
+        <v>0.05388877894799053</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1167207369194486</v>
+        <v>0.06764901456407298</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9503480996186271</v>
+        <v>0.9046244072891382</v>
       </c>
       <c r="I58" t="n">
-        <v>0.003988825374165986</v>
+        <v>0.002218961625275317</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>405</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-1.953</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4.209705041178492</v>
+      </c>
+      <c r="E59" t="n">
+        <v>570.0712366886015</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.1493343698306212</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.575801012779596</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.9019257393243121</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.2909904487746087</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>419</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.736</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5.370392937443722</v>
+      </c>
+      <c r="E60" t="n">
+        <v>570.0682047925649</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1467922405474358</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.976055310844055</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.9219155434954192</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.3663434472976715</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>433</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1.519</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6.682660005027197</v>
+      </c>
+      <c r="E61" t="n">
+        <v>570.066642111457</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.1425568629173084</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2.38796210143742</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.9401858073820889</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.4181943636601003</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>447</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.302</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7.869908983136606</v>
+      </c>
+      <c r="E62" t="n">
+        <v>570.0666476691864</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.1380009807939097</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2.72233656793363</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.9491338364682516</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.4769860134938911</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>461</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-1.085</v>
+      </c>
+      <c r="D63" t="n">
+        <v>9.062204821574904</v>
+      </c>
+      <c r="E63" t="n">
+        <v>570.0703498897996</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.1328719139085701</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.018262435514481</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.9502060252152897</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.6017329179478046</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>475</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.868</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10.10055690473268</v>
+      </c>
+      <c r="E64" t="n">
+        <v>570.0723377120632</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.1285717632935712</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3.255223813785248</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.9542164793158761</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.6698966312814806</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>489</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.651</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10.85439359584672</v>
+      </c>
+      <c r="E65" t="n">
+        <v>570.0757127346998</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.1256821594118796</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3.419551381868509</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.9565770113870212</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.718507998766804</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>503</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.434</v>
+      </c>
+      <c r="D66" t="n">
+        <v>11.74233721308104</v>
+      </c>
+      <c r="E66" t="n">
+        <v>570.0799237725362</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.1214957383071792</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3.576066010650957</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.9582972042775777</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.7853601992480552</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>517</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.217</v>
+      </c>
+      <c r="D67" t="n">
+        <v>12.33688043850126</v>
+      </c>
+      <c r="E67" t="n">
+        <v>570.0842262516934</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.1172138518435928</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3.62471802807044</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.9608771467545244</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.7890956800992818</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>531</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>12.99836614260124</v>
+      </c>
+      <c r="E68" t="n">
+        <v>570.0899209023908</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.1116718102448124</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3.638498972604626</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.961526733712236</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.8315800570554487</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>558</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="D69" t="n">
+        <v>12.99982690533966</v>
+      </c>
+      <c r="E69" t="n">
+        <v>570.097360418966</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.1100068602001778</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3.584654250141681</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.958684888001199</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.8872945172047918</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>585</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="D70" t="n">
+        <v>12.47756371006743</v>
+      </c>
+      <c r="E70" t="n">
+        <v>570.108352837971</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.1052038016449428</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3.290418694767547</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.9519007683465319</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.9286407507433011</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>612</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1.2555</v>
+      </c>
+      <c r="D71" t="n">
+        <v>12.00324971256994</v>
+      </c>
+      <c r="E71" t="n">
+        <v>570.1197516176436</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.09493104844408419</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2.856255493410781</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.9592910884905813</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.6737407737424502</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>639</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="D72" t="n">
+        <v>10.78257838371021</v>
+      </c>
+      <c r="E72" t="n">
+        <v>570.1321662173585</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.08699491060849056</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.351291123307431</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.9653641616529312</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.4349937908451932</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>666</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2.0925</v>
+      </c>
+      <c r="D73" t="n">
+        <v>7.806686307345391</v>
+      </c>
+      <c r="E73" t="n">
+        <v>570.1475489013294</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.08082959698706847</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1.581710786312855</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.9599623770719403</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.2484952607034909</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>693</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4.847248027390126</v>
+      </c>
+      <c r="E74" t="n">
+        <v>570.1624202488384</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.07287949448558956</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.8855040020501044</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.9651327544412538</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.07579742574279917</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>720</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2.9295</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2.666678222981447</v>
+      </c>
+      <c r="E75" t="n">
+        <v>570.1753524369897</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.06441748234123064</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.4305903529848945</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.9764601027776993</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.01377923248101014</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>747</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3.348</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1.237619154424388</v>
+      </c>
+      <c r="E76" t="n">
+        <v>570.1991252463777</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.05721449740278144</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.1774937412630091</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.9734339011578148</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.00316244809516258</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cu I 570.0 nm</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>774</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3.7665</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.5471250109497697</v>
+      </c>
+      <c r="E77" t="n">
+        <v>570.2175460158546</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.05893716330542895</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.08082872561510374</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.9061738147710052</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.002050874874511463</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>515</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.403</v>
+      </c>
+      <c r="D78" t="n">
+        <v>54.76251421220876</v>
+      </c>
+      <c r="E78" t="n">
+        <v>578.2852673338375</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.128571453204235</v>
+      </c>
+      <c r="G78" t="n">
+        <v>17.64890907601071</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.9003045388220188</v>
+      </c>
+      <c r="I78" t="n">
+        <v>32.83332673590399</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>517</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.372</v>
+      </c>
+      <c r="D79" t="n">
+        <v>55.29141626226706</v>
+      </c>
+      <c r="E79" t="n">
+        <v>578.285932939639</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.1276919163767841</v>
+      </c>
+      <c r="G79" t="n">
+        <v>17.69746464228114</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.9021007898980009</v>
+      </c>
+      <c r="I79" t="n">
+        <v>32.61565490236659</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>520</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.3255</v>
+      </c>
+      <c r="D80" t="n">
+        <v>55.95290590414368</v>
+      </c>
+      <c r="E80" t="n">
+        <v>578.2868641583567</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.1264155564808627</v>
+      </c>
+      <c r="G80" t="n">
+        <v>17.73017823399465</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.9036400808688743</v>
+      </c>
+      <c r="I80" t="n">
+        <v>32.55379388116937</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>523</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.279</v>
+      </c>
+      <c r="D81" t="n">
+        <v>56.56200241988056</v>
+      </c>
+      <c r="E81" t="n">
+        <v>578.288070228677</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.1250237062230441</v>
+      </c>
+      <c r="G81" t="n">
+        <v>17.72585038320461</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.9039846331505459</v>
+      </c>
+      <c r="I81" t="n">
+        <v>32.83128290842748</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>526</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.2325</v>
+      </c>
+      <c r="D82" t="n">
+        <v>57.10646518770071</v>
+      </c>
+      <c r="E82" t="n">
+        <v>578.2893585640605</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.1238483133347084</v>
+      </c>
+      <c r="G82" t="n">
+        <v>17.72822721845196</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.9045021987189016</v>
+      </c>
+      <c r="I82" t="n">
+        <v>33.00568159166805</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>529</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.186</v>
+      </c>
+      <c r="D83" t="n">
+        <v>57.75624041487428</v>
+      </c>
+      <c r="E83" t="n">
+        <v>578.2910220281746</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.1222195928396844</v>
+      </c>
+      <c r="G83" t="n">
+        <v>17.69414908932152</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.9070544276788505</v>
+      </c>
+      <c r="I83" t="n">
+        <v>32.40534912588438</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>532</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.1395</v>
+      </c>
+      <c r="D84" t="n">
+        <v>58.36719361005192</v>
+      </c>
+      <c r="E84" t="n">
+        <v>578.2926432596947</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.1206263694848665</v>
+      </c>
+      <c r="G84" t="n">
+        <v>17.64822383608046</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.9077353258131421</v>
+      </c>
+      <c r="I84" t="n">
+        <v>32.4709608678754</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>535</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.093</v>
+      </c>
+      <c r="D85" t="n">
+        <v>58.78857373258143</v>
+      </c>
+      <c r="E85" t="n">
+        <v>578.2936145394178</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.1196999963001072</v>
+      </c>
+      <c r="G85" t="n">
+        <v>17.63912326163487</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.9086425305686421</v>
+      </c>
+      <c r="I85" t="n">
+        <v>32.38391741425243</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>538</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.0465</v>
+      </c>
+      <c r="D86" t="n">
+        <v>59.08668729042689</v>
+      </c>
+      <c r="E86" t="n">
+        <v>578.294218863567</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.119112341654093</v>
+      </c>
+      <c r="G86" t="n">
+        <v>17.64153369922084</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.9100637212422382</v>
+      </c>
+      <c r="I86" t="n">
+        <v>32.02202597736087</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>541</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>59.34656565856318</v>
+      </c>
+      <c r="E87" t="n">
+        <v>578.294940082597</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.1185438280696145</v>
+      </c>
+      <c r="G87" t="n">
+        <v>17.63455372258793</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.9111795972575392</v>
+      </c>
+      <c r="I87" t="n">
+        <v>31.72912389673714</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>571</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="D88" t="n">
+        <v>57.61604816350911</v>
+      </c>
+      <c r="E88" t="n">
+        <v>578.3020500266753</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.1149532653870797</v>
+      </c>
+      <c r="G88" t="n">
+        <v>16.60178226391579</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.927582810265581</v>
+      </c>
+      <c r="I88" t="n">
+        <v>23.39083798151988</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>602</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.9455</v>
+      </c>
+      <c r="D89" t="n">
+        <v>56.01828211991815</v>
+      </c>
+      <c r="E89" t="n">
+        <v>578.3153179963707</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.1054551086912979</v>
+      </c>
+      <c r="G89" t="n">
+        <v>14.80769103668698</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.9588514053857458</v>
+      </c>
+      <c r="I89" t="n">
+        <v>11.36955705583438</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>633</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="D90" t="n">
+        <v>48.24018223658896</v>
+      </c>
+      <c r="E90" t="n">
+        <v>578.3278582652748</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.1026339208294939</v>
+      </c>
+      <c r="G90" t="n">
+        <v>12.41051472280261</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.9751698646892698</v>
+      </c>
+      <c r="I90" t="n">
+        <v>4.949572842533592</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>663</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="D91" t="n">
+        <v>34.50864864907635</v>
+      </c>
+      <c r="E91" t="n">
+        <v>578.3492424557746</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.100064032283525</v>
+      </c>
+      <c r="G91" t="n">
+        <v>8.655574257527594</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.9605430847693004</v>
+      </c>
+      <c r="I91" t="n">
+        <v>4.020665365629294</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>694</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2.3715</v>
+      </c>
+      <c r="D92" t="n">
+        <v>21.6088690384105</v>
+      </c>
+      <c r="E92" t="n">
+        <v>578.3785147813423</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.08523115601604997</v>
+      </c>
+      <c r="G92" t="n">
+        <v>4.61657983829117</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.9390650629642397</v>
+      </c>
+      <c r="I92" t="n">
+        <v>2.159161260576258</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>725</v>
+      </c>
+      <c r="C93" t="n">
+        <v>2.852</v>
+      </c>
+      <c r="D93" t="n">
+        <v>11.93375574296815</v>
+      </c>
+      <c r="E93" t="n">
+        <v>578.3993550164888</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.06564466617896078</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1.963661036930261</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.96549562189848</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.2845080152660189</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>755</v>
+      </c>
+      <c r="C94" t="n">
+        <v>3.317</v>
+      </c>
+      <c r="D94" t="n">
+        <v>5.058220998424588</v>
+      </c>
+      <c r="E94" t="n">
+        <v>578.4103730587458</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.06452556413804918</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.8181247751676027</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.9817175868083821</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.02642975668110635</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>786</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3.7975</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2.098232159738975</v>
+      </c>
+      <c r="E95" t="n">
+        <v>578.4367593138585</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.06388498468387614</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.3360023140521944</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.9690403705066799</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.007614365647306901</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Cu I 578.2 nm</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>817</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4.278</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.8113776053377774</v>
+      </c>
+      <c r="E96" t="n">
+        <v>578.4661356865878</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.07962385583882221</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.1619407534675333</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.9022544121235602</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.004128154375414759</v>
       </c>
     </row>
   </sheetData>
